--- a/data/trans_orig/BARTHEL_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/BARTHEL_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2007</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25718</t>
+          <t>26516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46880</t>
+          <t>47574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66478</t>
+          <t>66608</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99550</t>
+          <t>101561</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99096</t>
+          <t>100984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>140662</t>
+          <t>139695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326309</t>
+          <t>325615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>347471</t>
+          <t>346673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>488199</t>
+          <t>486188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>521271</t>
+          <t>521141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>820276</t>
+          <t>821243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>861842</t>
+          <t>859954</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>797</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>81261</t>
+          <t>80507</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87290</t>
+          <t>87286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50625</t>
+          <t>51163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60187</t>
+          <t>60153</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135292</t>
+          <t>135811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>146639</t>
+          <t>146573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32914</t>
+          <t>34132</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>25941</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>57002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66891</t>
+          <t>66757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>29182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53228</t>
+          <t>52301</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74229</t>
+          <t>73382</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111261</t>
+          <t>109071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112046</t>
+          <t>109799</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155501</t>
+          <t>153994</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>449238</t>
+          <t>450165</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>472568</t>
+          <t>473284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>565581</t>
+          <t>567771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>602613</t>
+          <t>603460</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1023807</t>
+          <t>1025314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1067262</t>
+          <t>1069509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2012</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57908</t>
+          <t>57219</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92805</t>
+          <t>93393</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151779</t>
+          <t>151409</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>198192</t>
+          <t>196866</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>219164</t>
+          <t>217432</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>279772</t>
+          <t>275967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,31%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>321593</t>
+          <t>321005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>356490</t>
+          <t>357179</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>436353</t>
+          <t>437679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>482766</t>
+          <t>483136</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>769170</t>
+          <t>772975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>829778</t>
+          <t>831510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,27%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15895</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>20638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31369</t>
+          <t>31086</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>103408</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114753</t>
+          <t>114776</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62638</t>
+          <t>62436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75666</t>
+          <t>76355</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170370</t>
+          <t>170653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188367</t>
+          <t>188263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>21242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39167</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47686</t>
+          <t>47724</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65298</t>
+          <t>65275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103386</t>
+          <t>101241</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166287</t>
+          <t>166415</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>214870</t>
+          <t>216209</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>243978</t>
+          <t>242545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>304183</t>
+          <t>305102</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>456251</t>
+          <t>458396</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>494339</t>
+          <t>494362</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>524995</t>
+          <t>523656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>573578</t>
+          <t>573450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>995319</t>
+          <t>994400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1055524</t>
+          <t>1056957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,34%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2016</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44245</t>
+          <t>43813</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70036</t>
+          <t>70045</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119412</t>
+          <t>121140</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164977</t>
+          <t>164156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>172638</t>
+          <t>171638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>225403</t>
+          <t>224066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283865</t>
+          <t>283856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309656</t>
+          <t>310088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>389780</t>
+          <t>390601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>435345</t>
+          <t>433617</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>683255</t>
+          <t>684592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>736020</t>
+          <t>737020</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16341</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38477</t>
+          <t>37217</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25288</t>
+          <t>24216</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50674</t>
+          <t>48612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174587</t>
+          <t>174704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186955</t>
+          <t>186530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149597</t>
+          <t>150857</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171733</t>
+          <t>171522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>329932</t>
+          <t>331994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>355318</t>
+          <t>356390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32811</t>
+          <t>33154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41247</t>
+          <t>41249</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63955</t>
+          <t>64797</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74302</t>
+          <t>74812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57152</t>
+          <t>55918</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86788</t>
+          <t>84730</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143113</t>
+          <t>143689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>196400</t>
+          <t>194142</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210433</t>
+          <t>210183</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>268645</t>
+          <t>266732</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>501675</t>
+          <t>503733</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>531311</t>
+          <t>532545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>580105</t>
+          <t>582363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>633392</t>
+          <t>632816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1096323</t>
+          <t>1098236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1154535</t>
+          <t>1154785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,6%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel) en 2023</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44706</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65140</t>
+          <t>65207</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>135822</t>
+          <t>135682</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164792</t>
+          <t>164420</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>187583</t>
+          <t>186616</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>224113</t>
+          <t>223941</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>202246</t>
+          <t>202179</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222680</t>
+          <t>222322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>330309</t>
+          <t>330681</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>359279</t>
+          <t>359419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>538373</t>
+          <t>538545</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574903</t>
+          <t>575870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17584</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33176</t>
+          <t>32920</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60281</t>
+          <t>60520</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24385</t>
+          <t>24712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81676</t>
+          <t>82415</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>240081</t>
+          <t>240337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>255673</t>
+          <t>255137</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>395111</t>
+          <t>394872</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445923</t>
+          <t>445030</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646973</t>
+          <t>646234</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>704264</t>
+          <t>703937</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11100</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93886</t>
+          <t>93806</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102002</t>
+          <t>102360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62316</t>
+          <t>62122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68616</t>
+          <t>68698</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159850</t>
+          <t>159641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169711</t>
+          <t>169637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72293</t>
+          <t>70247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98371</t>
+          <t>98613</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99957</t>
+          <t>99120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>242202</t>
+          <t>240901</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167092</t>
+          <t>172775</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>315732</t>
+          <t>316800</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>547257</t>
+          <t>547015</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>573335</t>
+          <t>575381</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>779615</t>
+          <t>780916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>921860</t>
+          <t>922697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1351713</t>
+          <t>1350645</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1500353</t>
+          <t>1494670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/BARTHEL_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/BARTHEL_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26516</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47574</t>
+          <t>47375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66608</t>
+          <t>66770</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101561</t>
+          <t>100717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100984</t>
+          <t>98038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139695</t>
+          <t>140042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>325615</t>
+          <t>325814</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>346673</t>
+          <t>346853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>486188</t>
+          <t>487032</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>521141</t>
+          <t>520979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>821243</t>
+          <t>820896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>859954</t>
+          <t>862900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80507</t>
+          <t>81492</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87286</t>
+          <t>87308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51163</t>
+          <t>50887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60153</t>
+          <t>60230</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>135811</t>
+          <t>135461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>146573</t>
+          <t>146508</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34132</t>
+          <t>34934</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19203</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25941</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57002</t>
+          <t>56805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66757</t>
+          <t>66817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29182</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52301</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73382</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109071</t>
+          <t>111199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109799</t>
+          <t>110431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>153994</t>
+          <t>153159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>450165</t>
+          <t>448530</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>473284</t>
+          <t>471304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>567771</t>
+          <t>565643</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>603460</t>
+          <t>601344</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1025314</t>
+          <t>1026149</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1069509</t>
+          <t>1068877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57219</t>
+          <t>57342</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93393</t>
+          <t>91265</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151409</t>
+          <t>150716</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>196866</t>
+          <t>196636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>217432</t>
+          <t>218923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>275967</t>
+          <t>277208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>321005</t>
+          <t>323133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>357179</t>
+          <t>357056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>437679</t>
+          <t>437909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>483136</t>
+          <t>483829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>772975</t>
+          <t>771734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>831510</t>
+          <t>830019</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,13%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15257</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31086</t>
+          <t>31629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103408</t>
+          <t>102558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114776</t>
+          <t>114755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62436</t>
+          <t>61963</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76355</t>
+          <t>75715</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170653</t>
+          <t>170110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188263</t>
+          <t>188646</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47724</t>
+          <t>47708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65275</t>
+          <t>67035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101241</t>
+          <t>102984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166415</t>
+          <t>165925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>216209</t>
+          <t>213176</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242545</t>
+          <t>243090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>305102</t>
+          <t>304591</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>458396</t>
+          <t>456653</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>494362</t>
+          <t>492602</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>523656</t>
+          <t>526689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>573450</t>
+          <t>573940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>994400</t>
+          <t>994911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1056957</t>
+          <t>1056412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43813</t>
+          <t>43991</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70045</t>
+          <t>69938</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121140</t>
+          <t>121585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164156</t>
+          <t>165475</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>171638</t>
+          <t>175531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>224066</t>
+          <t>224550</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283856</t>
+          <t>283963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310088</t>
+          <t>309910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390601</t>
+          <t>389282</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>433617</t>
+          <t>433172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>684592</t>
+          <t>684108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>737020</t>
+          <t>733127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17828</t>
+          <t>17794</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37217</t>
+          <t>39056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>25559</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48612</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174704</t>
+          <t>174738</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186530</t>
+          <t>186464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150857</t>
+          <t>149018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171522</t>
+          <t>171584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>331994</t>
+          <t>330692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>356390</t>
+          <t>355047</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10906</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33154</t>
+          <t>32652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41249</t>
+          <t>41254</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64797</t>
+          <t>64621</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74812</t>
+          <t>74352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55918</t>
+          <t>56480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84730</t>
+          <t>85265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>143689</t>
+          <t>145222</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194142</t>
+          <t>196379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210183</t>
+          <t>208197</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>266732</t>
+          <t>267927</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>503733</t>
+          <t>503198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>532545</t>
+          <t>531983</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>582363</t>
+          <t>580126</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>632816</t>
+          <t>631283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1098236</t>
+          <t>1097041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1154785</t>
+          <t>1156771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>54476</t>
+          <t>57250</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45064</t>
+          <t>46711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65207</t>
+          <t>68454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>149688</t>
+          <t>162297</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>135682</t>
+          <t>147487</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>164420</t>
+          <t>179491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>204164</t>
+          <t>219548</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>186616</t>
+          <t>200980</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223941</t>
+          <t>242123</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>212910</t>
+          <t>230686</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>202179</t>
+          <t>219482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222322</t>
+          <t>241225</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>345413</t>
+          <t>370621</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>330681</t>
+          <t>353427</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>359419</t>
+          <t>385431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>558322</t>
+          <t>601306</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>538545</t>
+          <t>578731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575870</t>
+          <t>619874</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>267386</t>
+          <t>287936</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>267386</t>
+          <t>287936</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>267386</t>
+          <t>287936</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>495101</t>
+          <t>532918</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>495101</t>
+          <t>532918</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>495101</t>
+          <t>532918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>762486</t>
+          <t>820854</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>762486</t>
+          <t>820854</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>762486</t>
+          <t>820854</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24397</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18120</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32920</t>
+          <t>35743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31186</t>
+          <t>36568</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>29518</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60520</t>
+          <t>46147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>55583</t>
+          <t>62494</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24712</t>
+          <t>52589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82415</t>
+          <t>76222</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>248860</t>
+          <t>277899</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>240337</t>
+          <t>268082</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>255137</t>
+          <t>284657</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>424206</t>
+          <t>240733</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>394872</t>
+          <t>231154</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>445030</t>
+          <t>247783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>673066</t>
+          <t>518632</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646234</t>
+          <t>504904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>703937</t>
+          <t>528537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>455392</t>
+          <t>277301</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>455392</t>
+          <t>277301</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>455392</t>
+          <t>277301</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>728649</t>
+          <t>581126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>728649</t>
+          <t>581126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>728649</t>
+          <t>581126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>99325</t>
+          <t>112280</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93806</t>
+          <t>106019</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102360</t>
+          <t>115667</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66078</t>
+          <t>77168</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62122</t>
+          <t>72946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68698</t>
+          <t>80001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>165403</t>
+          <t>189449</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159641</t>
+          <t>182110</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169637</t>
+          <t>194079</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84534</t>
+          <t>89777</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70247</t>
+          <t>77265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98613</t>
+          <t>105146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>186121</t>
+          <t>204552</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99120</t>
+          <t>184180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>240901</t>
+          <t>222619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>270655</t>
+          <t>294329</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>172775</t>
+          <t>271487</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316800</t>
+          <t>322485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>561094</t>
+          <t>620866</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>547015</t>
+          <t>605497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>575381</t>
+          <t>633378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>835696</t>
+          <t>688522</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>780916</t>
+          <t>670455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>922697</t>
+          <t>708894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1396790</t>
+          <t>1309387</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1350645</t>
+          <t>1281231</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1494670</t>
+          <t>1332229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>83,07%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>645628</t>
+          <t>710643</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>645628</t>
+          <t>710643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>645628</t>
+          <t>710643</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1021817</t>
+          <t>893074</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1021817</t>
+          <t>893074</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1021817</t>
+          <t>893074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1667445</t>
+          <t>1603716</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1667445</t>
+          <t>1603716</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1667445</t>
+          <t>1603716</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
